--- a/codelists/BC_respiratory_outcomes_codelist_checklist_all.xlsx
+++ b/codelists/BC_respiratory_outcomes_codelist_checklist_all.xlsx
@@ -1,51 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\BC_respiratory_public\codelists\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59F7B0D-B95C-49F4-B47B-B1ED20907002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="cr_codelist_asthma_aurum.do" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cr_codelist_bmi_aurum.do" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cr_codelist_bronchiectasis_auru" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cr_codelist_copd_aurum.do" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cr_codelist_cvdgrouped_aurum.do" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="cr_codelist_diabetes_aurum.do" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cr_codelist_hypertension_medica" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="cr_codelist_ild_aurum.do" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="cr_codelist_multiple_sclerosis_" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="cr_codelist_smoking_aurum.do" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="all_combined" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="cr_codelist_asthma_aurum.do" sheetId="1" r:id="rId1"/>
+    <sheet name="cr_codelist_bmi_aurum.do" sheetId="2" r:id="rId2"/>
+    <sheet name="cr_codelist_bronchiectasis_auru" sheetId="3" r:id="rId3"/>
+    <sheet name="cr_codelist_copd_aurum.do" sheetId="4" r:id="rId4"/>
+    <sheet name="cr_codelist_cvdgrouped_aurum.do" sheetId="5" r:id="rId5"/>
+    <sheet name="cr_codelist_diabetes_aurum.do" sheetId="6" r:id="rId6"/>
+    <sheet name="cr_codelist_hypertension_medica" sheetId="7" r:id="rId7"/>
+    <sheet name="cr_codelist_ild_aurum.do" sheetId="8" r:id="rId8"/>
+    <sheet name="cr_codelist_multiple_sclerosis_" sheetId="9" r:id="rId9"/>
+    <sheet name="cr_codelist_smoking_aurum.do" sheetId="10" r:id="rId10"/>
+    <sheet name="all_combined" sheetId="11" r:id="rId11"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
-  <si>
-    <t xml:space="preserve">header</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subheader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">item_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">information</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3706" uniqueCount="357">
+  <si>
+    <t>header</t>
+  </si>
+  <si>
+    <t>subheader</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>item_name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>information</t>
   </si>
   <si>
     <t xml:space="preserve">Metadata </t>
   </si>
   <si>
-    <t xml:space="preserve">0a</t>
+    <t>0a</t>
   </si>
   <si>
     <t xml:space="preserve"> Name </t>
@@ -54,10 +62,10 @@
     <t xml:space="preserve">What is the name of the codelist? </t>
   </si>
   <si>
-    <t xml:space="preserve">Asthma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0b</t>
+    <t>Asthma</t>
+  </si>
+  <si>
+    <t>0b</t>
   </si>
   <si>
     <t xml:space="preserve"> Author(s) </t>
@@ -66,10 +74,10 @@
     <t xml:space="preserve">Who created the codelist? </t>
   </si>
   <si>
-    <t xml:space="preserve">Kirsty Andresen for BC_respiratory outcomes (based on JQ's validated codelist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0c</t>
+    <t>Kirsty Andresen for BC_respiratory outcomes (based on JQ's validated codelist)</t>
+  </si>
+  <si>
+    <t>0c</t>
   </si>
   <si>
     <t xml:space="preserve"> Date finalised </t>
@@ -78,10 +86,10 @@
     <t xml:space="preserve">When was the codelist finalised? </t>
   </si>
   <si>
-    <t xml:space="preserve">23/08/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0d</t>
+    <t>23/08/2025</t>
+  </si>
+  <si>
+    <t>0d</t>
   </si>
   <si>
     <t xml:space="preserve"> Target data source </t>
@@ -90,10 +98,10 @@
     <t xml:space="preserve">What data is the codelist designed to be used with? </t>
   </si>
   <si>
-    <t xml:space="preserve">CPRD AURUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0e</t>
+    <t>CPRD AURUM</t>
+  </si>
+  <si>
+    <t>0e</t>
   </si>
   <si>
     <t xml:space="preserve"> Terminology </t>
@@ -102,7 +110,7 @@
     <t xml:space="preserve">What is the terminology? (e.g., SNOMED, ICD) </t>
   </si>
   <si>
-    <t xml:space="preserve">SNOMED CT (mapped to CPRD MedCodeId)</t>
+    <t>SNOMED CT (mapped to CPRD MedCodeId)</t>
   </si>
   <si>
     <t xml:space="preserve">Define a clinical concept </t>
@@ -111,7 +119,7 @@
     <t xml:space="preserve">Define </t>
   </si>
   <si>
-    <t xml:space="preserve">1a</t>
+    <t>1a</t>
   </si>
   <si>
     <t xml:space="preserve"> Concept </t>
@@ -120,7 +128,7 @@
     <t xml:space="preserve">What is the clinical concept (e.g., the disease, drug, test result, etc…) of interest? </t>
   </si>
   <si>
-    <t xml:space="preserve">1b</t>
+    <t>1b</t>
   </si>
   <si>
     <t xml:space="preserve"> Timeframe </t>
@@ -129,10 +137,10 @@
     <t xml:space="preserve">Should the codelist capture new, current, and/or previous events? </t>
   </si>
   <si>
-    <t xml:space="preserve">New (incident) and previous/current (prevalent) events, as categorized within the codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1c</t>
+    <t>New (incident) and previous/current (prevalent) events, as categorized within the codelist.</t>
+  </si>
+  <si>
+    <t>1c</t>
   </si>
   <si>
     <t xml:space="preserve"> Accuracy </t>
@@ -141,10 +149,10 @@
     <t xml:space="preserve">Should the codelist capture probable or definite codes? </t>
   </si>
   <si>
-    <t xml:space="preserve">The codelist primarily aims to capture definite codes. Terms indicating uncertainty like 'suspected' are excluded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1d</t>
+    <t>The codelist primarily aims to capture definite codes. Terms indicating uncertainty like 'suspected' are excluded.</t>
+  </si>
+  <si>
+    <t>1d</t>
   </si>
   <si>
     <t xml:space="preserve"> Setting </t>
@@ -153,7 +161,7 @@
     <t xml:space="preserve">What is the (health care) setting (e.g., primary care, hospital care)? </t>
   </si>
   <si>
-    <t xml:space="preserve">UK primary care</t>
+    <t>UK primary care</t>
   </si>
   <si>
     <t xml:space="preserve">Identify and evaluate existing codelists </t>
@@ -162,7 +170,7 @@
     <t xml:space="preserve">Search </t>
   </si>
   <si>
-    <t xml:space="preserve">2a</t>
+    <t>2a</t>
   </si>
   <si>
     <t xml:space="preserve"> Sources searched </t>
@@ -171,10 +179,10 @@
     <t xml:space="preserve">Which sources were searched (e.g., internet search, codelist repositories)? </t>
   </si>
   <si>
-    <t xml:space="preserve">A previously validated codelist by JQ was used as a primary source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2b</t>
+    <t>A previously validated codelist by JQ was used as a primary source.</t>
+  </si>
+  <si>
+    <t>2b</t>
   </si>
   <si>
     <t xml:space="preserve"> Existing codelists found </t>
@@ -183,13 +191,13 @@
     <t xml:space="preserve">Which suitable codelists did you find? </t>
   </si>
   <si>
-    <t xml:space="preserve">A validated codelist for definite asthma (definite_asthma_JQ.dta) created by JQ.</t>
+    <t>A validated codelist for definite asthma (definite_asthma_JQ.dta) created by JQ.</t>
   </si>
   <si>
     <t xml:space="preserve">Verify </t>
   </si>
   <si>
-    <t xml:space="preserve">3a</t>
+    <t>3a</t>
   </si>
   <si>
     <t xml:space="preserve"> Verified by others </t>
@@ -198,7 +206,7 @@
     <t xml:space="preserve">Which information is available to verify the quality of suitable codelists? </t>
   </si>
   <si>
-    <t xml:space="preserve">The primary existing codelist was previously validated by JQ.</t>
+    <t>The primary existing codelist was previously validated by JQ.</t>
   </si>
   <si>
     <t xml:space="preserve"> Verified by yourself </t>
@@ -207,13 +215,13 @@
     <t xml:space="preserve">Which checks did you conduct to verify the quality of suitable codelists? </t>
   </si>
   <si>
-    <t xml:space="preserve">A comparison was conducted against the existing JQ codelist, with identified differences in terms of codes kept and dropped being documented with justifications.</t>
+    <t>A comparison was conducted against the existing JQ codelist, with identified differences in terms of codes kept and dropped being documented with justifications.</t>
   </si>
   <si>
     <t xml:space="preserve">Reference </t>
   </si>
   <si>
-    <t xml:space="preserve">4a</t>
+    <t>4a</t>
   </si>
   <si>
     <t xml:space="preserve"> Existing codelists used </t>
@@ -222,7 +230,7 @@
     <t xml:space="preserve">Are you making use of any existing codelists? If yes, reference these, and specify how they are being used. </t>
   </si>
   <si>
-    <t xml:space="preserve">A previously validated codelist, 'definite_asthma_JQ.dta', was used as a baseline and for cross-checking during the iterative refinement process.</t>
+    <t>A previously validated codelist, 'definite_asthma_JQ.dta', was used as a baseline and for cross-checking during the iterative refinement process.</t>
   </si>
   <si>
     <t xml:space="preserve">Create a new codelist </t>
@@ -231,7 +239,7 @@
     <t xml:space="preserve">Prepare </t>
   </si>
   <si>
-    <t xml:space="preserve">5a</t>
+    <t>5a</t>
   </si>
   <si>
     <t xml:space="preserve"> Synonyms </t>
@@ -240,10 +248,10 @@
     <t xml:space="preserve">What are synonyms and related words for the clinical concept (e.g., different names for a disease/drug) and how did you identify these (e.g., source of clinical knowledge)? </t>
   </si>
   <si>
-    <t xml:space="preserve">The primary search term was 'asthma'. No specific synonyms were explicitly listed for initial search beyond the core concept, but the process involved comparing against a previously validated codelist which would encompass common related terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5b</t>
+    <t>The primary search term was 'asthma'. No specific synonyms were explicitly listed for initial search beyond the core concept, but the process involved comparing against a previously validated codelist which would encompass common related terms.</t>
+  </si>
+  <si>
+    <t>5b</t>
   </si>
   <si>
     <t xml:space="preserve"> Exceptions </t>
@@ -252,13 +260,13 @@
     <t xml:space="preserve">What should not be included in the codelist? </t>
   </si>
   <si>
-    <t xml:space="preserve">Codes related to administration, communication, logistics, community, trials, family history, childhood, screening, prevention, QoF, persistent, resolved/stable/intermittent states, seasonal, nocturnal, daily, suspected, overlap syndromes, comorbidities (e.g., cardiac, industrial, fungal, thunderstorm, pregnancy), infective/poisoning, specific treatments (e.g., steroid-dependent, drug-induced), adverse reactions, monitoring, study-related terms, education, risk assessment, negations (e.g., 'asthma not', 'no change', 'never'), referrals, and short codes/catch-alls were excluded.</t>
+    <t>Codes related to administration, communication, logistics, community, trials, family history, childhood, screening, prevention, QoF, persistent, resolved/stable/intermittent states, seasonal, nocturnal, daily, suspected, overlap syndromes, comorbidities (e.g., cardiac, industrial, fungal, thunderstorm, pregnancy), infective/poisoning, specific treatments (e.g., steroid-dependent, drug-induced), adverse reactions, monitoring, study-related terms, education, risk assessment, negations (e.g., 'asthma not', 'no change', 'never'), referrals, and short codes/catch-alls were excluded.</t>
   </si>
   <si>
     <t xml:space="preserve">Create </t>
   </si>
   <si>
-    <t xml:space="preserve">6a</t>
+    <t>6a</t>
   </si>
   <si>
     <t xml:space="preserve"> Method used </t>
@@ -267,10 +275,10 @@
     <t xml:space="preserve">Which method (e.g., a script, a tool) did you use to create the draft codelist? </t>
   </si>
   <si>
-    <t xml:space="preserve">A Stata do-file was used, employing a script ('searchMedicalDict.do') to perform word searches on the SNOMED code dictionary and string matching for inclusions and exclusions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6b</t>
+    <t>A Stata do-file was used, employing a script ('searchMedicalDict.do') to perform word searches on the SNOMED code dictionary and string matching for inclusions and exclusions.</t>
+  </si>
+  <si>
+    <t>6b</t>
   </si>
   <si>
     <t xml:space="preserve"> Search terms </t>
@@ -279,10 +287,10 @@
     <t xml:space="preserve">Which search terms, and if applicable, exclusion terms did you use? </t>
   </si>
   <si>
-    <t xml:space="preserve">Search term: '*asthma*'. Exclusion terms include: '*monitoring sms*', '*invit*', '*letter*', '*call*', '*sms*', '*telephone*', '*admin*', '*report*', '*assessment using*', '*action care planning*', '*asthma*clinic*', '*nurs*', '*diary*', '*telehealth*', '*giv*', '*offer*', '*society member*', '*family history*', '*fh*', '*h/o*', '*history*', '*childhood*', '*screening*', '*prophylactic*', '*qof*', '*excepted from asthma quality indicators*', '*at risk of*', '*persistent*', '*resolved*', '*stable*', '*intermittent*', '*seasonal asthma*', '*nocturnal*', '*daily*', '*less*than*', '*dormant*', '*suspected*', '*overlap*', '*co-occurent*', '*co-occurrent*', '*asthmatic bronchitis*', '*obstruct*', '*obsruct*', '*mixed*', '*cardiac*', '*industrial*', '*fungal*', '*thunderstorm*', '*pregnancy*', '*infective*', '*poisoning*', '*oral steroid-dependent asthma*', '*steroid dependent asthma*', '*drug-induced*', '*substance induced asthma*', '*adverse*', `aspirin-induced`, '*asthma study*', '*cough variant*', '*asthma control step 0*', '*control test*', '*education*', '*risk* assessment', '*manchester triage*', '*trial*', '*asthma*monitoring*status*', `follow-up asthma assessment`, '*control questionnaire*', '*asthma monitoring due*', `asthma monitoring in*`, `asthma care`, '*asthma not*', '*referral*', '*declined*', '*did not*', '*deleted*', '*not done*', '*refus*', '*never*', '*no change*', '*no asthma trigger*', '*not wkly*', '*acq*', '*rfc*', '*rcp*', '*factitious*', '*rcf*', '*date of*', '*registration for access to online asthma self-management application*', `does not have asthma management plan`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6c</t>
+    <t>Search term: '*asthma*'. Exclusion terms include: '*monitoring sms*', '*invit*', '*letter*', '*call*', '*sms*', '*telephone*', '*admin*', '*report*', '*assessment using*', '*action care planning*', '*asthma*clinic*', '*nurs*', '*diary*', '*telehealth*', '*giv*', '*offer*', '*society member*', '*family history*', '*fh*', '*h/o*', '*history*', '*childhood*', '*screening*', '*prophylactic*', '*qof*', '*excepted from asthma quality indicators*', '*at risk of*', '*persistent*', '*resolved*', '*stable*', '*intermittent*', '*seasonal asthma*', '*nocturnal*', '*daily*', '*less*than*', '*dormant*', '*suspected*', '*overlap*', '*co-occurent*', '*co-occurrent*', '*asthmatic bronchitis*', '*obstruct*', '*obsruct*', '*mixed*', '*cardiac*', '*industrial*', '*fungal*', '*thunderstorm*', '*pregnancy*', '*infective*', '*poisoning*', '*oral steroid-dependent asthma*', '*steroid dependent asthma*', '*drug-induced*', '*substance induced asthma*', '*adverse*', `aspirin-induced`, '*asthma study*', '*cough variant*', '*asthma control step 0*', '*control test*', '*education*', '*risk* assessment', '*manchester triage*', '*trial*', '*asthma*monitoring*status*', `follow-up asthma assessment`, '*control questionnaire*', '*asthma monitoring due*', `asthma monitoring in*`, `asthma care`, '*asthma not*', '*referral*', '*declined*', '*did not*', '*deleted*', '*not done*', '*refus*', '*never*', '*no change*', '*no asthma trigger*', '*not wkly*', '*acq*', '*rfc*', '*rcp*', '*factitious*', '*rcf*', '*date of*', '*registration for access to online asthma self-management application*', `does not have asthma management plan`.</t>
+  </si>
+  <si>
+    <t>6c</t>
   </si>
   <si>
     <t xml:space="preserve"> Hierarchy used to extend search </t>
@@ -291,10 +299,10 @@
     <t xml:space="preserve">Did you use a dictionary hierarchy (e.g., ICD-10 chapters, SNOMED-CT concepts) to modify your search? If yes, specify. </t>
   </si>
   <si>
-    <t xml:space="preserve">The primary method involved textual search; no explicit dictionary hierarchy traversal was mentioned for extending the search.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6d</t>
+    <t>The primary method involved textual search; no explicit dictionary hierarchy traversal was mentioned for extending the search.</t>
+  </si>
+  <si>
+    <t>6d</t>
   </si>
   <si>
     <t xml:space="preserve"> Decisions made while iterating </t>
@@ -303,10 +311,10 @@
     <t xml:space="preserve">Which decisions did you make while iteratively refining the draft codelist? </t>
   </si>
   <si>
-    <t xml:space="preserve">Decisions were made by comparing the generated codelist against a previously validated JQ codelist. Specific codes from the JQ codelist were dropped (e.g., control tests, administrative terms, negations, chronic/persistent asthma, mixed asthma) and new codes were kept (e.g., acute/allergic/intrinsic/occupational asthma, specific triggers, asthma findings) with documented justifications for each inclusion/exclusion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6e</t>
+    <t>Decisions were made by comparing the generated codelist against a previously validated JQ codelist. Specific codes from the JQ codelist were dropped (e.g., control tests, administrative terms, negations, chronic/persistent asthma, mixed asthma) and new codes were kept (e.g., acute/allergic/intrinsic/occupational asthma, specific triggers, asthma findings) with documented justifications for each inclusion/exclusion.</t>
+  </si>
+  <si>
+    <t>6e</t>
   </si>
   <si>
     <t xml:space="preserve">(Optional) Categories </t>
@@ -315,7 +323,7 @@
     <t xml:space="preserve">Did you specify subcategories within the codelist? If yes, specify. </t>
   </si>
   <si>
-    <t xml:space="preserve">Yes, subcategories for 'incident' (dx_inc) and 'prevalent' (prev) codes were specified based on whether a code indicated a new event or a current/previous event.</t>
+    <t>Yes, subcategories for 'incident' (dx_inc) and 'prevalent' (prev) codes were specified based on whether a code indicated a new event or a current/previous event.</t>
   </si>
   <si>
     <t xml:space="preserve">Review, finalise and publish </t>
@@ -324,7 +332,7 @@
     <t xml:space="preserve">Review </t>
   </si>
   <si>
-    <t xml:space="preserve">7a</t>
+    <t>7a</t>
   </si>
   <si>
     <t xml:space="preserve"> Reviewers </t>
@@ -333,10 +341,10 @@
     <t xml:space="preserve">Who reviewed the codelist and what expertise did reviewers have? </t>
   </si>
   <si>
-    <t xml:space="preserve">The codelist was developed by Kirsty Andresen, based on a previously validated codelist by JQ. The changes and exclusions were documented during the development process.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7b</t>
+    <t>The codelist was developed by Kirsty Andresen, based on a previously validated codelist by JQ. The changes and exclusions were documented during the development process.</t>
+  </si>
+  <si>
+    <t>7b</t>
   </si>
   <si>
     <t xml:space="preserve"> Scope of review </t>
@@ -345,10 +353,10 @@
     <t xml:space="preserve">What was reviewed (Just the draft codelist or also the method, terms, etc..)? </t>
   </si>
   <si>
-    <t xml:space="preserve">The draft codelist and the search/exclusion terms were reviewed through comparison with a previously validated codelist, with specific discrepancies documented.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7c</t>
+    <t>The draft codelist and the search/exclusion terms were reviewed through comparison with a previously validated codelist, with specific discrepancies documented.</t>
+  </si>
+  <si>
+    <t>7c</t>
   </si>
   <si>
     <t xml:space="preserve"> Evidence of review </t>
@@ -357,13 +365,13 @@
     <t xml:space="preserve">Where is the review process documented? </t>
   </si>
   <si>
-    <t xml:space="preserve">The review process and decisions made are documented within the Stata do-file in the 'NOTES: DIFFERENCES FROM ORIGINAL CODELIST (AUG 2025)' section.</t>
+    <t>The review process and decisions made are documented within the Stata do-file in the 'NOTES: DIFFERENCES FROM ORIGINAL CODELIST (AUG 2025)' section.</t>
   </si>
   <si>
     <t xml:space="preserve">Checks </t>
   </si>
   <si>
-    <t xml:space="preserve">8a</t>
+    <t>8a</t>
   </si>
   <si>
     <t xml:space="preserve"> Internal checks </t>
@@ -372,10 +380,10 @@
     <t xml:space="preserve">What method(s) were used for internal checks, if any, and what are the findings? </t>
   </si>
   <si>
-    <t xml:space="preserve">not defined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8b</t>
+    <t>not defined</t>
+  </si>
+  <si>
+    <t>8b</t>
   </si>
   <si>
     <t xml:space="preserve"> External checks </t>
@@ -387,7 +395,7 @@
     <t xml:space="preserve">Publish </t>
   </si>
   <si>
-    <t xml:space="preserve">9a</t>
+    <t>9a</t>
   </si>
   <si>
     <t xml:space="preserve"> Codelist published </t>
@@ -396,10 +404,10 @@
     <t xml:space="preserve">Where is the codelist published? </t>
   </si>
   <si>
-    <t xml:space="preserve">Likely within a GitHub repository, as indicated by the file path reference 'C:\Github\BC_data_management\1 codelists\'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9b</t>
+    <t>Likely within a GitHub repository, as indicated by the file path reference 'C:\Github\BC_data_management\1 codelists\'.</t>
+  </si>
+  <si>
+    <t>9b</t>
   </si>
   <si>
     <t xml:space="preserve"> Resources published </t>
@@ -408,127 +416,127 @@
     <t xml:space="preserve">Where are the resources used to create the codelist (e.g., scripts, list of terms)? </t>
   </si>
   <si>
-    <t xml:space="preserve">The Stata do-file containing the search terms, exclusion terms, logic, and the final codelist (.dta file) are saved in the '$codelists/' directory, presumably within the same GitHub repository.</t>
+    <t>The Stata do-file containing the search terms, exclusion terms, logic, and the final codelist (.dta file) are saved in the '$codelists/' directory, presumably within the same GitHub repository.</t>
   </si>
   <si>
     <t xml:space="preserve">Name </t>
   </si>
   <si>
-    <t xml:space="preserve">Body Mass Index (BMI) Codelist</t>
+    <t>Body Mass Index (BMI) Codelist</t>
   </si>
   <si>
     <t xml:space="preserve">Author(s) </t>
   </si>
   <si>
-    <t xml:space="preserve">Helen Strongman</t>
+    <t>Helen Strongman</t>
   </si>
   <si>
     <t xml:space="preserve">Date finalised </t>
   </si>
   <si>
-    <t xml:space="preserve">06/10/2020</t>
+    <t>06/10/2020</t>
   </si>
   <si>
     <t xml:space="preserve">Target data source </t>
   </si>
   <si>
-    <t xml:space="preserve">CPRD Aurum</t>
+    <t>CPRD Aurum</t>
   </si>
   <si>
     <t xml:space="preserve">Terminology </t>
   </si>
   <si>
-    <t xml:space="preserve">SNOMED CT and Read codes</t>
+    <t>SNOMED CT and Read codes</t>
   </si>
   <si>
     <t xml:space="preserve">Concept </t>
   </si>
   <si>
-    <t xml:space="preserve">Body Mass Index (BMI)</t>
+    <t>Body Mass Index (BMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Timeframe </t>
   </si>
   <si>
-    <t xml:space="preserve">Current and previous events</t>
+    <t>Current and previous events</t>
   </si>
   <si>
     <t xml:space="preserve">Accuracy </t>
   </si>
   <si>
-    <t xml:space="preserve">Probable or definite codes</t>
+    <t>Probable or definite codes</t>
   </si>
   <si>
     <t xml:space="preserve">Setting </t>
   </si>
   <si>
-    <t xml:space="preserve">Primary care</t>
+    <t>Primary care</t>
   </si>
   <si>
     <t xml:space="preserve">Sources searched </t>
   </si>
   <si>
-    <t xml:space="preserve">Existing codelists (Tarita's CPRD code list, Harriet's LSHTM codelist) for comparison</t>
+    <t>Existing codelists (Tarita's CPRD code list, Harriet's LSHTM codelist) for comparison</t>
   </si>
   <si>
     <t xml:space="preserve">Existing codelists found </t>
   </si>
   <si>
-    <t xml:space="preserve">Tarita's CPRD code list and codelist developed by Harriet at LSHTM</t>
+    <t>Tarita's CPRD code list and codelist developed by Harriet at LSHTM</t>
   </si>
   <si>
     <t xml:space="preserve">Verified by others </t>
   </si>
   <si>
-    <t xml:space="preserve">3b</t>
+    <t>3b</t>
   </si>
   <si>
     <t xml:space="preserve">Verified by yourself </t>
   </si>
   <si>
-    <t xml:space="preserve">Comparison with Tarita's CPRD codelist and Harriet's LSHTM codelist</t>
+    <t>Comparison with Tarita's CPRD codelist and Harriet's LSHTM codelist</t>
   </si>
   <si>
     <t xml:space="preserve">Existing codelists used </t>
   </si>
   <si>
-    <t xml:space="preserve">Yes, Tarita's CPRD code list and Harriet's LSHTM codelist were used for comparison and development.</t>
+    <t>Yes, Tarita's CPRD code list and Harriet's LSHTM codelist were used for comparison and development.</t>
   </si>
   <si>
     <t xml:space="preserve">Synonyms </t>
   </si>
   <si>
-    <t xml:space="preserve">Terms from `BMI_codelist_comparison.txt` used as keyword terms for SNOMED codes.</t>
+    <t>Terms from `BMI_codelist_comparison.txt` used as keyword terms for SNOMED codes.</t>
   </si>
   <si>
     <t xml:space="preserve">Exceptions </t>
   </si>
   <si>
-    <t xml:space="preserve">Codes covering target weight (except for 'target weight reached'), percentiles, centiles, and both height and weight measurements.</t>
+    <t>Codes covering target weight (except for 'target weight reached'), percentiles, centiles, and both height and weight measurements.</t>
   </si>
   <si>
     <t xml:space="preserve">Method used </t>
   </si>
   <si>
-    <t xml:space="preserve">Stata script using keyword search and exclusion terms.</t>
+    <t>Stata script using keyword search and exclusion terms.</t>
   </si>
   <si>
     <t xml:space="preserve">Search terms </t>
   </si>
   <si>
-    <t xml:space="preserve">Search terms are keyword terms from an imported BMI codelist (`BMI_codelist_comparison.txt`). Exclusion terms used were: 'target', 'centile', 'percent', 'height weight'.</t>
+    <t>Search terms are keyword terms from an imported BMI codelist (`BMI_codelist_comparison.txt`). Exclusion terms used were: 'target', 'centile', 'percent', 'height weight'.</t>
   </si>
   <si>
     <t xml:space="preserve">Hierarchy used to extend search </t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
+    <t>No</t>
   </si>
   <si>
     <t xml:space="preserve">Decisions made while iterating </t>
   </si>
   <si>
-    <t xml:space="preserve">Initially excluded 'target' related terms, but 'target weight reached' was specifically re-included.</t>
+    <t>Initially excluded 'target' related terms, but 'target weight reached' was specifically re-included.</t>
   </si>
   <si>
     <t xml:space="preserve">Reviewers </t>
@@ -537,85 +545,85 @@
     <t xml:space="preserve">Scope of review </t>
   </si>
   <si>
-    <t xml:space="preserve">The draft codelist (codes and terms) was reviewed through comparison with existing codelists.</t>
+    <t>The draft codelist (codes and terms) was reviewed through comparison with existing codelists.</t>
   </si>
   <si>
     <t xml:space="preserve">Evidence of review </t>
   </si>
   <si>
-    <t xml:space="preserve">Within the Stata capture log file (`cr_codelist_bmi_aurum.txt`) and implied by the comparison with other codelists mentioned.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparison of the derived codelist's terms/codes with Tarita's CPRD code list and Harriet's LSHTM codelist; results are the generated `bmi` flag for matching SNOMED codes, after applying inclusion/exclusion criteria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External checks</t>
+    <t>Within the Stata capture log file (`cr_codelist_bmi_aurum.txt`) and implied by the comparison with other codelists mentioned.</t>
+  </si>
+  <si>
+    <t>Checks</t>
+  </si>
+  <si>
+    <t>Internal checks</t>
+  </si>
+  <si>
+    <t>Comparison of the derived codelist's terms/codes with Tarita's CPRD code list and Harriet's LSHTM codelist; results are the generated `bmi` flag for matching SNOMED codes, after applying inclusion/exclusion criteria.</t>
+  </si>
+  <si>
+    <t>External checks</t>
   </si>
   <si>
     <t xml:space="preserve">Codelist published </t>
   </si>
   <si>
-    <t xml:space="preserve">Saved to local data directory (`$datadir\cr_codelist_bmi_aurum`); not externally published in a repository.</t>
+    <t>Saved to local data directory (`$datadir\cr_codelist_bmi_aurum`); not externally published in a repository.</t>
   </si>
   <si>
     <t xml:space="preserve">Resources published </t>
   </si>
   <si>
-    <t xml:space="preserve">Stata script (`cr_codelist_bmi_aurum.do`) and source terms (`BMI_codelist_comparison.txt`) are saved in local study directories.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronchiectasis Codelist for CPRD Aurum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirsty Andresen for BC_respiratory outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPRD AURUM primary care database</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronchiectasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current and/or previous events related to bronchiectasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definite codes for bronchiectasis, based on JQ's validated codelist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UK primary care setting (CPRD Aurum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical dictionary (likely SNOMED/Read codes) through `searchMedicalDict.do` script; JQ's validated codelist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JQ's validated definite bronchiectasis codelist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The codelist is stated to be 'BASED ON JQs validated codelist', implying prior validation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparison of the search results with JQ's validated definite bronchiectasis codelist, and documentation of differences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JQ's validated definite bronchiectasis codelist, used as a reference for comparison and cross-checking during the development of the new codelist.</t>
+    <t>Stata script (`cr_codelist_bmi_aurum.do`) and source terms (`BMI_codelist_comparison.txt`) are saved in local study directories.</t>
+  </si>
+  <si>
+    <t>Bronchiectasis Codelist for CPRD Aurum</t>
+  </si>
+  <si>
+    <t>Kirsty Andresen for BC_respiratory outcomes</t>
+  </si>
+  <si>
+    <t>CPRD AURUM primary care database</t>
+  </si>
+  <si>
+    <t>Bronchiectasis</t>
+  </si>
+  <si>
+    <t>Current and/or previous events related to bronchiectasis</t>
+  </si>
+  <si>
+    <t>Definite codes for bronchiectasis, based on JQ's validated codelist</t>
+  </si>
+  <si>
+    <t>UK primary care setting (CPRD Aurum)</t>
+  </si>
+  <si>
+    <t>Medical dictionary (likely SNOMED/Read codes) through `searchMedicalDict.do` script; JQ's validated codelist</t>
+  </si>
+  <si>
+    <t>JQ's validated definite bronchiectasis codelist</t>
+  </si>
+  <si>
+    <t>The codelist is stated to be 'BASED ON JQs validated codelist', implying prior validation.</t>
+  </si>
+  <si>
+    <t>Comparison of the search results with JQ's validated definite bronchiectasis codelist, and documentation of differences.</t>
+  </si>
+  <si>
+    <t>JQ's validated definite bronchiectasis codelist, used as a reference for comparison and cross-checking during the development of the new codelist.</t>
   </si>
   <si>
     <t xml:space="preserve">What are synonyms and related words for the clinical concept (e.g., different names for a disease/drug) and how did you identify these (e.g., source of clinical knowledge)?  </t>
   </si>
   <si>
-    <t xml:space="preserve">The primary search term is 'bronchiectasis' using a wildcard search (`*bronchiectasis*`). Additional terms such as 'acquired bronchiectasis', 'adult bronchiectasis', and 'cylindrical bronchiectasis' were identified as part of the concept.</t>
+    <t>The primary search term is 'bronchiectasis' using a wildcard search (`*bronchiectasis*`). Additional terms such as 'acquired bronchiectasis', 'adult bronchiectasis', and 'cylindrical bronchiectasis' were identified as part of the concept.</t>
   </si>
   <si>
     <t xml:space="preserve">What should not be included in the codelist?  </t>
   </si>
   <si>
-    <t xml:space="preserve">Codes containing terms like 'cystic fibrosis', 'h/o' (history of), 'exacerbation', 'co-occurrent', 'obstructive', and 'traction' were explicitly excluded. Codes from JQ's list not found by the search terms (e.g., 'bronchiectasis, chronic sinusitis and dextrocardia syndrome', 'developmental bronchiectasis') were implicitly excluded.</t>
+    <t>Codes containing terms like 'cystic fibrosis', 'h/o' (history of), 'exacerbation', 'co-occurrent', 'obstructive', and 'traction' were explicitly excluded. Codes from JQ's list not found by the search terms (e.g., 'bronchiectasis, chronic sinusitis and dextrocardia syndrome', 'developmental bronchiectasis') were implicitly excluded.</t>
   </si>
   <si>
     <t xml:space="preserve">Create  </t>
@@ -624,139 +632,139 @@
     <t xml:space="preserve">Which method (e.g., a script, a tool) did you use to create the draft codelist?  </t>
   </si>
   <si>
-    <t xml:space="preserve">A Stata script (`cr_codelist_bronchiectasis_aurum.do`) was used to perform a word search on the SNOMED code dictionary, employing inclusion and exclusion terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search term: '*bronchiectasis*'. Exclusion terms: '*cystic fibrosis*', '*h/o*', '*exacerbation*', '*co-occurrent*', '*obstructive*', '*traction*'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No explicit use of a dictionary hierarchy to extend the search was documented in the provided script, which primarily used a word search based on literal term matching.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisions were documented during the comparison with JQ's codelist: codes present in JQ's list but not found by the search were not included. Codes found by the search but not in JQ's list (e.g., 'acquired bronchiectasis', 'adult bronchiectasis', 'cylindrical bronchiectasis') were kept after review. Codes matching exclusion terms were removed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, a category named 'out_cat' was created, with '0' for 'dx_inc' (diagnosis incident) and '1' for 'prev' (prevalent).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The draft codelist and the search and exclusion terms were reviewed by comparing against JQ's validated codelist, with documented differences and rationale for inclusion/exclusion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The review process and documented differences are embedded within the `cr_codelist_bronchiectasis_aurum.do` script.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The codelist was internally checked by comparing its terms against JQ's validated codelist to verify inclusions and exclusions. Specific findings on differences are documented within the script.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No explicit external checks were performed on the final codelist beyond its development being based on JQ's previously validated codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPD (Chronic Obstructive Pulmonary Disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/08/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chronic Obstructive Pulmonary Disease (COPD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New (incident) and current/previous (prevalent) events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primarily definite codes based on the JQ codelist; however, some codes with 'nos' (not otherwise specified) or related to exacerbations are also included.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary care (CPRD AURUM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNOMED code dictionary (linked to CPRD Aurum medcodeid), comparison with existing 'definite_COPD_JQ' codelist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An existing 'definite_COPD_JQ' codelist was found and used for comparison.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The existing codelist (`definite_COPD_JQ`) is described as 'validated', implying it has been verified by others.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparison and manual review against the `definite_COPD_JQ` codelist, noting codes included/excluded and reasons for differences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, the existing 'definite_COPD_JQ' codelist was used as a reference for comparison and to refine the current codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synonyms and related terms include: 'copd', 'coad', 'chronic obstructive disease', 'chronic bronchitis', 'emphysema', 'chronic obst. pulm. dis. nos', 'chr. airway obstruction nos', 'airways obstructn irreversible', 'bronchitis with airway obstruction', 'chron obstruct pulmonary dis*'. These were identified through initial searches and comparison with the JQ codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terms related to admin/communication/logistics (e.g., invitation, letter), history/family history, pregnancy, other co-occurring conditions (e.g., asthma, interstitial), screening/prevention, uncertainty/temporal aspects (e.g., resolved, suspected), monitoring, or explicit negations (e.g., no copd).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stata scripts, including `searchMedicalDict.do`, were used for word search of the SNOMED code dictionary and applying exclusion terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search terms: 'copd', 'coad', 'chronic obstructive disease', 'chronic bronchitis', 'emphysema', 'chronic obst. pulm. dis. nos', 'chr. airway obstruction nos', 'airways obstructn irreversible', 'bronchitis with airway obstruction', 'chron obstruct pulmonary dis*'. Exclusion terms (e.g.): 'invita', 'letter', 'family history', 'with asthma', 'screening', 'resolved', 'suspected', 'no copd' (a comprehensive list of exclusion terms was used, categorized by administrative, historical, co-morbid, screening, temporal, monitoring, and negation criteria).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisions involved dropping codes from the initial JQ codelist that referred to administrative processes, healthcare professional interactions, care pathways, or non-patient interactions. Codes referring to exacerbations, 'not otherwise specified' terms, and review statuses were kept from the search results even if not in the JQ codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, codes were subcategorized by 'emphysema' and 'chronic bronchitis' flags. Additionally, codes were categorized as 'incident' or 'prevalent'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirsty Andresen (codelist author) reviewed the codelist by comparing it against the 'definite_COPD_JQ' validated codelist, identifying differences and providing justifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both the draft codelist (including individual codes) and the search/exclusion terms were reviewed by comparing against an existing codelist and documenting differences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The review process and decisions made during iteration are documented within the `cr_codelist_copd_aurum.do` file itself.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal checks included counting codes after filtering (`count`) and cross-tabulating the merge results (`tab _m copd, m`). An assertion was used to confirm that all codes have incident and prevalent flags (`assert incident !=. &amp; prevalent !=.`). No specific findings (e.g., number of observations) from the target database are detailed in the provided script, unlike the PDF's Table 2 example.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External checks involved merging and comparing the generated codelist with the `definite_COPD_JQ` codelist. Findings, documented in the 'NOTES' section of the script, highlighted differences where codes from JQ's list were dropped (e.g., administrative terms) and codes not in JQ's list were kept (e.g., exacerbations, 'nos' terms).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The codelist is saved to `$codelists/cr_codelist_copd_aurum.dta`, which is likely part of a GitHub repository, as indicated by the path `C:\Github\BC_data_management`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Stata script (`cr_codelist_copd_aurum.do`), which includes the search and exclusion terms, is saved to `C:\Github\BC_data_management\1 codelists` and would be considered the published resource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grouped Cardiovascular Disease (CVD) Codelist (CR Codelist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krishnan (based on file path) or not defined from the script directly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPRD MedCodeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grouped Cardiovascular Disease (CVD), combining arrhythmia, angina, coronary artery disease (CAD), myocardial infarction (MI), sudden cardiac arrest (SCA), revascularisation, non-specific CVD, heart failure (HF), stroke, venous thromboembolism (VTE), deep vein thrombosis (DVT), pulmonary embolism, cardiomyopathy, pericarditis, valvular heart disease (VHD), and peripheral vascular disease (PVD).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Individual codelists for arrhythmia, angina, cad, mi, sca, revascularisation, nonspecificcvd, hf, stroke, vte, dvt, pulmonaryembolism, cardiomyopathy, pericarditis, vhd, pvd (e.g., cr_codelist_arrhythmia_aurum).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The codelist is created by combining existing codelists for individual CVD outcomes: cr_codelist_arrhythmia_aurum, cr_codelist_angina_aurum, cr_codelist_cad_aurum, cr_codelist_mi_aurum, cr_codelist_sca_aurum, cr_codelist_revascularisation_aurum, cr_codelist_nonspecificcvd_aurum, cr_codelist_hf_aurum, cr_codelist_stroke_aurum, cr_codelist_vte_aurum, cr_codelist_dvt_aurum, cr_codelist_pulmonaryembolism_aurum, cr_codelist_cardiomyopathy_aurum, cr_codelist_pericarditis_aurum, cr_codelist_vhd_aurum, cr_codelist_pvd_aurum. Each is appended to form the combined list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not defined for the grouped codelist, assumed handled in individual outcome codelists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Stata script was used to append multiple existing codelists and manage duplicates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The codelist combines existing codelists for the following outcomes: arrhythmia, angina, cad, mi, sca, revascularisation, nonspecificcvd, hf, stroke, vte, dvt, pulmonaryembolism, cardiomyopathy, pericarditis, vhd, pvd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not defined for the grouped codelist creation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicates in 'medcodeid' were removed using `duplicates drop medcodeid, force` after appending all individual codelists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, subcategories (e.g., 'arrhythmia', 'angina', 'cad') were specified using a 'cvd' variable to indicate the original contributing codelist for each medcodeid.</t>
+    <t>A Stata script (`cr_codelist_bronchiectasis_aurum.do`) was used to perform a word search on the SNOMED code dictionary, employing inclusion and exclusion terms.</t>
+  </si>
+  <si>
+    <t>Search term: '*bronchiectasis*'. Exclusion terms: '*cystic fibrosis*', '*h/o*', '*exacerbation*', '*co-occurrent*', '*obstructive*', '*traction*'.</t>
+  </si>
+  <si>
+    <t>No explicit use of a dictionary hierarchy to extend the search was documented in the provided script, which primarily used a word search based on literal term matching.</t>
+  </si>
+  <si>
+    <t>Decisions were documented during the comparison with JQ's codelist: codes present in JQ's list but not found by the search were not included. Codes found by the search but not in JQ's list (e.g., 'acquired bronchiectasis', 'adult bronchiectasis', 'cylindrical bronchiectasis') were kept after review. Codes matching exclusion terms were removed.</t>
+  </si>
+  <si>
+    <t>Yes, a category named 'out_cat' was created, with '0' for 'dx_inc' (diagnosis incident) and '1' for 'prev' (prevalent).</t>
+  </si>
+  <si>
+    <t>The draft codelist and the search and exclusion terms were reviewed by comparing against JQ's validated codelist, with documented differences and rationale for inclusion/exclusion.</t>
+  </si>
+  <si>
+    <t>The review process and documented differences are embedded within the `cr_codelist_bronchiectasis_aurum.do` script.</t>
+  </si>
+  <si>
+    <t>The codelist was internally checked by comparing its terms against JQ's validated codelist to verify inclusions and exclusions. Specific findings on differences are documented within the script.</t>
+  </si>
+  <si>
+    <t>No explicit external checks were performed on the final codelist beyond its development being based on JQ's previously validated codelist.</t>
+  </si>
+  <si>
+    <t>COPD (Chronic Obstructive Pulmonary Disease)</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>Chronic Obstructive Pulmonary Disease (COPD)</t>
+  </si>
+  <si>
+    <t>New (incident) and current/previous (prevalent) events</t>
+  </si>
+  <si>
+    <t>Primarily definite codes based on the JQ codelist; however, some codes with 'nos' (not otherwise specified) or related to exacerbations are also included.</t>
+  </si>
+  <si>
+    <t>Primary care (CPRD AURUM)</t>
+  </si>
+  <si>
+    <t>SNOMED code dictionary (linked to CPRD Aurum medcodeid), comparison with existing 'definite_COPD_JQ' codelist</t>
+  </si>
+  <si>
+    <t>An existing 'definite_COPD_JQ' codelist was found and used for comparison.</t>
+  </si>
+  <si>
+    <t>The existing codelist (`definite_COPD_JQ`) is described as 'validated', implying it has been verified by others.</t>
+  </si>
+  <si>
+    <t>Comparison and manual review against the `definite_COPD_JQ` codelist, noting codes included/excluded and reasons for differences.</t>
+  </si>
+  <si>
+    <t>Yes, the existing 'definite_COPD_JQ' codelist was used as a reference for comparison and to refine the current codelist.</t>
+  </si>
+  <si>
+    <t>Synonyms and related terms include: 'copd', 'coad', 'chronic obstructive disease', 'chronic bronchitis', 'emphysema', 'chronic obst. pulm. dis. nos', 'chr. airway obstruction nos', 'airways obstructn irreversible', 'bronchitis with airway obstruction', 'chron obstruct pulmonary dis*'. These were identified through initial searches and comparison with the JQ codelist.</t>
+  </si>
+  <si>
+    <t>Terms related to admin/communication/logistics (e.g., invitation, letter), history/family history, pregnancy, other co-occurring conditions (e.g., asthma, interstitial), screening/prevention, uncertainty/temporal aspects (e.g., resolved, suspected), monitoring, or explicit negations (e.g., no copd).</t>
+  </si>
+  <si>
+    <t>Stata scripts, including `searchMedicalDict.do`, were used for word search of the SNOMED code dictionary and applying exclusion terms.</t>
+  </si>
+  <si>
+    <t>Search terms: 'copd', 'coad', 'chronic obstructive disease', 'chronic bronchitis', 'emphysema', 'chronic obst. pulm. dis. nos', 'chr. airway obstruction nos', 'airways obstructn irreversible', 'bronchitis with airway obstruction', 'chron obstruct pulmonary dis*'. Exclusion terms (e.g.): 'invita', 'letter', 'family history', 'with asthma', 'screening', 'resolved', 'suspected', 'no copd' (a comprehensive list of exclusion terms was used, categorized by administrative, historical, co-morbid, screening, temporal, monitoring, and negation criteria).</t>
+  </si>
+  <si>
+    <t>Decisions involved dropping codes from the initial JQ codelist that referred to administrative processes, healthcare professional interactions, care pathways, or non-patient interactions. Codes referring to exacerbations, 'not otherwise specified' terms, and review statuses were kept from the search results even if not in the JQ codelist.</t>
+  </si>
+  <si>
+    <t>Yes, codes were subcategorized by 'emphysema' and 'chronic bronchitis' flags. Additionally, codes were categorized as 'incident' or 'prevalent'.</t>
+  </si>
+  <si>
+    <t>Kirsty Andresen (codelist author) reviewed the codelist by comparing it against the 'definite_COPD_JQ' validated codelist, identifying differences and providing justifications.</t>
+  </si>
+  <si>
+    <t>Both the draft codelist (including individual codes) and the search/exclusion terms were reviewed by comparing against an existing codelist and documenting differences.</t>
+  </si>
+  <si>
+    <t>The review process and decisions made during iteration are documented within the `cr_codelist_copd_aurum.do` file itself.</t>
+  </si>
+  <si>
+    <t>Internal checks included counting codes after filtering (`count`) and cross-tabulating the merge results (`tab _m copd, m`). An assertion was used to confirm that all codes have incident and prevalent flags (`assert incident !=. &amp; prevalent !=.`). No specific findings (e.g., number of observations) from the target database are detailed in the provided script, unlike the PDF's Table 2 example.</t>
+  </si>
+  <si>
+    <t>External checks involved merging and comparing the generated codelist with the `definite_COPD_JQ` codelist. Findings, documented in the 'NOTES' section of the script, highlighted differences where codes from JQ's list were dropped (e.g., administrative terms) and codes not in JQ's list were kept (e.g., exacerbations, 'nos' terms).</t>
+  </si>
+  <si>
+    <t>The codelist is saved to `$codelists/cr_codelist_copd_aurum.dta`, which is likely part of a GitHub repository, as indicated by the path `C:\Github\BC_data_management`.</t>
+  </si>
+  <si>
+    <t>The Stata script (`cr_codelist_copd_aurum.do`), which includes the search and exclusion terms, is saved to `C:\Github\BC_data_management\1 codelists` and would be considered the published resource.</t>
+  </si>
+  <si>
+    <t>Grouped Cardiovascular Disease (CVD) Codelist (CR Codelist)</t>
+  </si>
+  <si>
+    <t>Krishnan (based on file path) or not defined from the script directly</t>
+  </si>
+  <si>
+    <t>CPRD MedCodeId</t>
+  </si>
+  <si>
+    <t>Grouped Cardiovascular Disease (CVD), combining arrhythmia, angina, coronary artery disease (CAD), myocardial infarction (MI), sudden cardiac arrest (SCA), revascularisation, non-specific CVD, heart failure (HF), stroke, venous thromboembolism (VTE), deep vein thrombosis (DVT), pulmonary embolism, cardiomyopathy, pericarditis, valvular heart disease (VHD), and peripheral vascular disease (PVD).</t>
+  </si>
+  <si>
+    <t>Individual codelists for arrhythmia, angina, cad, mi, sca, revascularisation, nonspecificcvd, hf, stroke, vte, dvt, pulmonaryembolism, cardiomyopathy, pericarditis, vhd, pvd (e.g., cr_codelist_arrhythmia_aurum).</t>
+  </si>
+  <si>
+    <t>The codelist is created by combining existing codelists for individual CVD outcomes: cr_codelist_arrhythmia_aurum, cr_codelist_angina_aurum, cr_codelist_cad_aurum, cr_codelist_mi_aurum, cr_codelist_sca_aurum, cr_codelist_revascularisation_aurum, cr_codelist_nonspecificcvd_aurum, cr_codelist_hf_aurum, cr_codelist_stroke_aurum, cr_codelist_vte_aurum, cr_codelist_dvt_aurum, cr_codelist_pulmonaryembolism_aurum, cr_codelist_cardiomyopathy_aurum, cr_codelist_pericarditis_aurum, cr_codelist_vhd_aurum, cr_codelist_pvd_aurum. Each is appended to form the combined list.</t>
+  </si>
+  <si>
+    <t>not defined for the grouped codelist, assumed handled in individual outcome codelists.</t>
+  </si>
+  <si>
+    <t>A Stata script was used to append multiple existing codelists and manage duplicates.</t>
+  </si>
+  <si>
+    <t>The codelist combines existing codelists for the following outcomes: arrhythmia, angina, cad, mi, sca, revascularisation, nonspecificcvd, hf, stroke, vte, dvt, pulmonaryembolism, cardiomyopathy, pericarditis, vhd, pvd.</t>
+  </si>
+  <si>
+    <t>not defined for the grouped codelist creation.</t>
+  </si>
+  <si>
+    <t>Duplicates in 'medcodeid' were removed using `duplicates drop medcodeid, force` after appending all individual codelists.</t>
+  </si>
+  <si>
+    <t>Yes, subcategories (e.g., 'arrhythmia', 'angina', 'cad') were specified using a 'cvd' variable to indicate the original contributing codelist for each medcodeid.</t>
   </si>
   <si>
     <t xml:space="preserve">Internal checks </t>
@@ -765,342 +773,341 @@
     <t xml:space="preserve">External checks </t>
   </si>
   <si>
-    <t xml:space="preserve">The Stata script, which defines the list of outcomes and operations, is a resource used to create the codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diabetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helena Carreira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 February 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define a clinical concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New, current, and previous events (explicitly includes 'H/O diabetes' and monitors current cases).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probable and definite codes are included; some probable codes are categorized as 'Possible diabetes' (e.g., using 'suspected' terms).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identify and evaluate existing codelists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The primary explicit source mentioned is 'Rohini's code'. Other general search sources were not explicitly defined in the provided log.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A codelist from 'Rohini' was used as a basis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, this codelist is based on a previous codelist created by Rohini.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a new codelist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Various synonyms and related words for diabetes (e.g., IDDM, NIDDM, T1DM, T2DM, insulin-dependent, self-monitoring glucose, DM, hyperglycaemic non-ketotic coma) were identified and used as search terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codes related to non-diabetes, pre-diabetes, insulin antibodies, family history, poisoning, pregnancy, administrative terms (e.g., cadmium, DMSA, DHSS, DMARD), and specific terms like 'qdiabetes risk calculator', 'diabetes mellitus excluded', 'suspected diabetes mellitus', 'no h/o: diabetic nephropathy', 'no h/o hypoglycaemic event in diabetes', 'no h/o: diabetes mellitus' were excluded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stata script ('cr_codelist_diabetes_aurum.do' and 'searchMedicalDict.do') was used to search the Read Code dictionary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search terms: 'diabet*', 'iddm*', 'insulin*dependent*', 'insulin*dose*', 'niddm*', 't1dm*', 't2dm*', 'insulin*needles*', 'honk*', 'hypersomol*', 'self monitoring*glucose*', 'DM*', 'insulin*treatment*', 'insulin therapy*', 'hyperglycaemic non-ketotic coma*'. Exclusion terms: 'cadmium*', 'adm area*', 'dmsa*', 'grandmother*', 'aurumman*', 'dhss*', 'dmard*', 'amendm*', 'rast*', 'symbol*', 'o/e - no*', 'non-diabetes*', 'pre-diabet*', 'prediab*', 'insulin*antibody*', 'insipid*', 'family history*', 'fh*', 'child*', 'relative*', 'family*', 'poisoning*', 'leaflet*', 'requested*', 'wait*', 'at*risk*', 'preg/childb*', 'obstetric*', 'gestation*', 'fetus*', 'infant*', 'pregnan*', and specific terms like 'qdiabetes risk calculator', 'diabetes mellitus excluded', 'suspected diabetes mellitus', 'no h/o: diabetic nephropathy', 'no h/o hypoglycaemic event in diabetes', 'no h/o: diabetes mellitus'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not explicitly stated as used to extend search; a word search of the Read Code dictionary was performed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisions included iteratively refining search and exclusion terms, manual exclusion of specific unwanted codes, and categorizing codes into diabetes types (e.g., History of Diabetes, Possible Diabetes, Type 1, Type 2, Secondary, and NOS) based on keywords.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, subcategories were specified: 0. Diabetes not diagnosed, 1. H/O diabetes, 2. Possible diabetes, 3. T1DM, 4. T2DM, 5. Secondary DM, 6. DM, NOS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local storage: '$codelists\cr_codelist_diabetes_aurum.dta' and 'J:\EHR-Working\Krishnan\20_000268\codelists\Excel files for codelist checking\cr_codelist_diabetes_aurum.xlsx'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local storage: 'cr_codelist_diabetes_aurum.do' script and generated Excel file at 'J:\EHR-Working\Krishnan\20_000268\codelists\Excel files for codelist checking\cr_codelist_diabetes_aurum.xlsx'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypertension Codelist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shamsudeen Mohammed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1.0 01 08 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypertension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current and previous events.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both probable and definite codes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UK primary care.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synonyms include 'hyperten', 'high blood pressure', 'bp elevation'. Source of identification not defined.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codes related to non-systemic hypertension (e.g., ocular, portal, pulmonary, intracranial hypertension), pregnancy-related hypertension (e.g., gestational, pre-eclampsia), antihypertensive drug exposure/adverse events, and conditions not directly representing hypertension (e.g., family history, scores like CHA2DS2-VASc, 'no hypertension monitoring required').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stata script (cr_codelist_hypertension_medical_aurum.do) for word search and categorization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search terms: 'hyperten', 'high blood pressure', 'bp elevation'. Exclusion terms are concepts related to non-systemic hypertension, pregnancy-related hypertension, antihypertensive drug exposure/adverse events, and other conditions not directly representing hypertension (as identified and categorized in the Stata script).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No, a dictionary hierarchy was not explicitly used to extend the search. Terms were identified by string matching and then manually categorized.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisions were made to categorize and exclude specific terms to differentiate between systemic hypertension, non-systemic hypertension, pregnancy-related hypertension, antihypertensive drug effects, and conditions merely related to hypertension (e.g., family history, monitoring, screening, or risk scores).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, subcategories include 'History of hypertension', 'Possible hypertension', and 'Diagnosed hypertension' based on clinical context.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal check ('assert bp_category != "999"') was performed to ensure all identified terms were assigned to a category. No findings beyond this basic assertion are provided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Stata script (cr_codelist_hypertension_medical_aurum.do) and embedded search terms are resources, but their publication location is not defined. The codelist is saved locally.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interstitial Lung Disease (ILD) codelist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirsty Andresen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15th August 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPRD MedCodeId (mapped from SNOMED CT or Read codes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interstitial Lung Disease (ILD), including treatment-related, exposure-related, autoimmune-related ILD, and pulmonary fibrosis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New (incident) and/or current/previous (prevalent) events.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definite codes, with sub-categorisation for broad or narrow fibrosis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existing collaboration and networks (specifically, a codelist from Jenny Quint).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A codelist on definite ILD from Jenny Quint (definite_ild_JQ.dta).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, the definite_ild_JQ.dta codelist (from Jenny Quint) was used as the base codelist and subsequently categorised.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synonyms and related terms for Interstitial Lung Disease (ILD) were obtained from the existing definite_ild_JQ.dta codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Stata script was used to process and categorise an existing codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No new search or exclusion terms were used in this script; an existing codelist (definite_ild_JQ.dta) was imported.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisions included categorising codes into incident/prevalent (out_cat), broad/narrow fibrosis (certlevel), and specific ILD types (treatment-related, exposure-related, autoimmune-related, pulmonary fibrosis - ild_cat).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, subcategories include: incident/prevalent (out_cat), broad/narrow fibrosis (certlevel), and specific ILD types (treatment-related, exposure-related, autoimmune-related ILD, pulmonary fibrosis - ild_cat).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currently saved locally to '$codelists/cr_codelist_ild_aurum.dta'; public publication location not defined.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Stata script (cr_codelist_ild_aurum.do) and the base codelist (definite_ild_JQ.dta) are available locally within the project directory; public publication location for resources not defined.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple sclerosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 10 2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read codes (CPRD Aurum MedCodeId)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current and previous events, including various forms of multiple sclerosis and related management codes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definite codes, as 'suspected multiple sclerosis' is explicitly excluded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GitHub (https://github.com/spiros/chronological-map-phenotypes/tree/master/primary_care)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One codelist from https://github.com/spiros/chronological-map-phenotypes/tree/master/primary_care</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual classification of terms found in the dictionary, ensuring only definite multiple sclerosis codes are included and others (e.g., suspected, administrative) are excluded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, one existing codelist from https://github.com/spiros/chronological-map-phenotypes/tree/master/primary_care was used as a basis/starting point for this codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The primary search term was `*multiple*sclerosis*`. Other explicit synonyms or sources of clinical knowledge for identifying them beyond the initial base codelist are not defined.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neonatal multiple sclerosis, family history of multiple sclerosis, suspected multiple sclerosis, multiple sclerosis care plan agreed, multiple sclerosis monitoring letters/invitations, referral by MS nurse, Kurtzke rating scale, questionnaire completed, referral to community MS team.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Stata script was used to perform a word search in the medical dictionary, followed by manual classification of identified terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search term: `*multiple*sclerosis*`. Exclusion terms: `*neonatal*`, `*fh:*`, `*family*history*`, and specific manual exclusions like 'suspected multiple sclerosis'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terms identified by the word search were manually reviewed and categorized as definite multiple sclerosis (included) or non-definite/administrative (excluded). Examples include explicitly excluding 'suspected multiple sclerosis' and including various definite forms like 'relapsing remitting multiple sclerosis'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An `assert` command was used in the Stata script to ensure all identified terms were classified. However, no specific findings regarding prevalence or incidence within the dataset for the final codelist are reported.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No external checks performed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoking status codelist for CPRD Aurum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smoking status and related concepts (e.g., tobacco dependence, smoking cessation therapy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current and previous events, categorized into non-smoker, current smoker, and ex-smoker statuses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primarily definite codes, categorized into non-smoker, current smoker, ex-smoker, and current/ex-smoker statuses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CPRDAurumMedical dictionary was searched for relevant terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An existing codelist named 'smoking_aurum_achim' (presumably from Helen) was identified and used for comparison.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The codelist was cross-checked against 'smoking_aurum_achim'. No explicit external verification information for 'smoking_aurum_achim' itself is provided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual review and categorization of individual terms were conducted. An assertion was used to check that all identified codes were classified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, an existing codelist named 'smoking_aurum_achim' was used to cross-check the newly created codelist categories.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keywords used for initial term identification include TOBACCO, NICOTINE, SMOK, CIGAR, BUPROPION, and PACK YEARS. These were identified through keyword search in the CPRDAurumMedical dictionary terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codes related to smoke inhalation, passive smoking, family history of smoking, adverse reactions to nicotine/bupropion not linked to cessation, smoke alarms, tobacco industry roles, and general exposure to smoke/fire were excluded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Stata script was used to identify terms by keywords, followed by manual categorization and refinement based on specific term matching.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search terms: TOBACCO, NICOTINE, SMOK, CIGAR, BUPROPION, PACK YEARS. Exclusion terms were implicitly defined by terms assigned as irrelevant (type=9) during manual review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No, the search was based on keywords and explicit term matching rather than dictionary hierarchy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terms were iteratively reviewed and manually assigned to categories (non-smoker, current smoker, ex-smoker, current/ex-smoker, or irrelevant) based on their clinical meaning. New codes were classified as they appeared during review.</t>
+    <t>The Stata script, which defines the list of outcomes and operations, is a resource used to create the codelist.</t>
+  </si>
+  <si>
+    <t>Metadata</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>Helena Carreira</t>
+  </si>
+  <si>
+    <t>26 February 2025</t>
+  </si>
+  <si>
+    <t>Define a clinical concept</t>
+  </si>
+  <si>
+    <t>Define</t>
+  </si>
+  <si>
+    <t>New, current, and previous events (explicitly includes 'H/O diabetes' and monitors current cases).</t>
+  </si>
+  <si>
+    <t>Probable and definite codes are included; some probable codes are categorized as 'Possible diabetes' (e.g., using 'suspected' terms).</t>
+  </si>
+  <si>
+    <t>Identify and evaluate existing codelists</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>The primary explicit source mentioned is 'Rohini's code'. Other general search sources were not explicitly defined in the provided log.</t>
+  </si>
+  <si>
+    <t>A codelist from 'Rohini' was used as a basis.</t>
+  </si>
+  <si>
+    <t>Verify</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Yes, this codelist is based on a previous codelist created by Rohini.</t>
+  </si>
+  <si>
+    <t>Create a new codelist</t>
+  </si>
+  <si>
+    <t>Prepare</t>
+  </si>
+  <si>
+    <t>Various synonyms and related words for diabetes (e.g., IDDM, NIDDM, T1DM, T2DM, insulin-dependent, self-monitoring glucose, DM, hyperglycaemic non-ketotic coma) were identified and used as search terms.</t>
+  </si>
+  <si>
+    <t>Codes related to non-diabetes, pre-diabetes, insulin antibodies, family history, poisoning, pregnancy, administrative terms (e.g., cadmium, DMSA, DHSS, DMARD), and specific terms like 'qdiabetes risk calculator', 'diabetes mellitus excluded', 'suspected diabetes mellitus', 'no h/o: diabetic nephropathy', 'no h/o hypoglycaemic event in diabetes', 'no h/o: diabetes mellitus' were excluded.</t>
+  </si>
+  <si>
+    <t>Stata script ('cr_codelist_diabetes_aurum.do' and 'searchMedicalDict.do') was used to search the Read Code dictionary.</t>
+  </si>
+  <si>
+    <t>Search terms: 'diabet*', 'iddm*', 'insulin*dependent*', 'insulin*dose*', 'niddm*', 't1dm*', 't2dm*', 'insulin*needles*', 'honk*', 'hypersomol*', 'self monitoring*glucose*', 'DM*', 'insulin*treatment*', 'insulin therapy*', 'hyperglycaemic non-ketotic coma*'. Exclusion terms: 'cadmium*', 'adm area*', 'dmsa*', 'grandmother*', 'aurumman*', 'dhss*', 'dmard*', 'amendm*', 'rast*', 'symbol*', 'o/e - no*', 'non-diabetes*', 'pre-diabet*', 'prediab*', 'insulin*antibody*', 'insipid*', 'family history*', 'fh*', 'child*', 'relative*', 'family*', 'poisoning*', 'leaflet*', 'requested*', 'wait*', 'at*risk*', 'preg/childb*', 'obstetric*', 'gestation*', 'fetus*', 'infant*', 'pregnan*', and specific terms like 'qdiabetes risk calculator', 'diabetes mellitus excluded', 'suspected diabetes mellitus', 'no h/o: diabetic nephropathy', 'no h/o hypoglycaemic event in diabetes', 'no h/o: diabetes mellitus'.</t>
+  </si>
+  <si>
+    <t>Not explicitly stated as used to extend search; a word search of the Read Code dictionary was performed.</t>
+  </si>
+  <si>
+    <t>Decisions included iteratively refining search and exclusion terms, manual exclusion of specific unwanted codes, and categorizing codes into diabetes types (e.g., History of Diabetes, Possible Diabetes, Type 1, Type 2, Secondary, and NOS) based on keywords.</t>
+  </si>
+  <si>
+    <t>Yes, subcategories were specified: 0. Diabetes not diagnosed, 1. H/O diabetes, 2. Possible diabetes, 3. T1DM, 4. T2DM, 5. Secondary DM, 6. DM, NOS.</t>
+  </si>
+  <si>
+    <t>Local storage: '$codelists\cr_codelist_diabetes_aurum.dta' and 'J:\EHR-Working\Krishnan\20_000268\codelists\Excel files for codelist checking\cr_codelist_diabetes_aurum.xlsx'.</t>
+  </si>
+  <si>
+    <t>Local storage: 'cr_codelist_diabetes_aurum.do' script and generated Excel file at 'J:\EHR-Working\Krishnan\20_000268\codelists\Excel files for codelist checking\cr_codelist_diabetes_aurum.xlsx'.</t>
+  </si>
+  <si>
+    <t>Hypertension Codelist</t>
+  </si>
+  <si>
+    <t>Shamsudeen Mohammed</t>
+  </si>
+  <si>
+    <t>v1.0 01 08 2025</t>
+  </si>
+  <si>
+    <t>Hypertension</t>
+  </si>
+  <si>
+    <t>Current and previous events.</t>
+  </si>
+  <si>
+    <t>Both probable and definite codes.</t>
+  </si>
+  <si>
+    <t>UK primary care.</t>
+  </si>
+  <si>
+    <t>Synonyms include 'hyperten', 'high blood pressure', 'bp elevation'. Source of identification not defined.</t>
+  </si>
+  <si>
+    <t>Codes related to non-systemic hypertension (e.g., ocular, portal, pulmonary, intracranial hypertension), pregnancy-related hypertension (e.g., gestational, pre-eclampsia), antihypertensive drug exposure/adverse events, and conditions not directly representing hypertension (e.g., family history, scores like CHA2DS2-VASc, 'no hypertension monitoring required').</t>
+  </si>
+  <si>
+    <t>Stata script (cr_codelist_hypertension_medical_aurum.do) for word search and categorization.</t>
+  </si>
+  <si>
+    <t>Search terms: 'hyperten', 'high blood pressure', 'bp elevation'. Exclusion terms are concepts related to non-systemic hypertension, pregnancy-related hypertension, antihypertensive drug exposure/adverse events, and other conditions not directly representing hypertension (as identified and categorized in the Stata script).</t>
+  </si>
+  <si>
+    <t>No, a dictionary hierarchy was not explicitly used to extend the search. Terms were identified by string matching and then manually categorized.</t>
+  </si>
+  <si>
+    <t>Decisions were made to categorize and exclude specific terms to differentiate between systemic hypertension, non-systemic hypertension, pregnancy-related hypertension, antihypertensive drug effects, and conditions merely related to hypertension (e.g., family history, monitoring, screening, or risk scores).</t>
+  </si>
+  <si>
+    <t>Yes, subcategories include 'History of hypertension', 'Possible hypertension', and 'Diagnosed hypertension' based on clinical context.</t>
+  </si>
+  <si>
+    <t>An internal check ('assert bp_category != "999"') was performed to ensure all identified terms were assigned to a category. No findings beyond this basic assertion are provided.</t>
+  </si>
+  <si>
+    <t>The Stata script (cr_codelist_hypertension_medical_aurum.do) and embedded search terms are resources, but their publication location is not defined. The codelist is saved locally.</t>
+  </si>
+  <si>
+    <t>Interstitial Lung Disease (ILD) codelist</t>
+  </si>
+  <si>
+    <t>Kirsty Andresen</t>
+  </si>
+  <si>
+    <t>15th August 2024</t>
+  </si>
+  <si>
+    <t>CPRD MedCodeId (mapped from SNOMED CT or Read codes)</t>
+  </si>
+  <si>
+    <t>Interstitial Lung Disease (ILD), including treatment-related, exposure-related, autoimmune-related ILD, and pulmonary fibrosis.</t>
+  </si>
+  <si>
+    <t>New (incident) and/or current/previous (prevalent) events.</t>
+  </si>
+  <si>
+    <t>Definite codes, with sub-categorisation for broad or narrow fibrosis.</t>
+  </si>
+  <si>
+    <t>Existing collaboration and networks (specifically, a codelist from Jenny Quint).</t>
+  </si>
+  <si>
+    <t>A codelist on definite ILD from Jenny Quint (definite_ild_JQ.dta).</t>
+  </si>
+  <si>
+    <t>Yes, the definite_ild_JQ.dta codelist (from Jenny Quint) was used as the base codelist and subsequently categorised.</t>
+  </si>
+  <si>
+    <t>Synonyms and related terms for Interstitial Lung Disease (ILD) were obtained from the existing definite_ild_JQ.dta codelist.</t>
+  </si>
+  <si>
+    <t>A Stata script was used to process and categorise an existing codelist.</t>
+  </si>
+  <si>
+    <t>No new search or exclusion terms were used in this script; an existing codelist (definite_ild_JQ.dta) was imported.</t>
+  </si>
+  <si>
+    <t>Decisions included categorising codes into incident/prevalent (out_cat), broad/narrow fibrosis (certlevel), and specific ILD types (treatment-related, exposure-related, autoimmune-related, pulmonary fibrosis - ild_cat).</t>
+  </si>
+  <si>
+    <t>Yes, subcategories include: incident/prevalent (out_cat), broad/narrow fibrosis (certlevel), and specific ILD types (treatment-related, exposure-related, autoimmune-related ILD, pulmonary fibrosis - ild_cat).</t>
+  </si>
+  <si>
+    <t>Currently saved locally to '$codelists/cr_codelist_ild_aurum.dta'; public publication location not defined.</t>
+  </si>
+  <si>
+    <t>The Stata script (cr_codelist_ild_aurum.do) and the base codelist (definite_ild_JQ.dta) are available locally within the project directory; public publication location for resources not defined.</t>
+  </si>
+  <si>
+    <t>Multiple sclerosis</t>
+  </si>
+  <si>
+    <t>25 10 2024</t>
+  </si>
+  <si>
+    <t>Read codes (CPRD Aurum MedCodeId)</t>
+  </si>
+  <si>
+    <t>Current and previous events, including various forms of multiple sclerosis and related management codes.</t>
+  </si>
+  <si>
+    <t>Definite codes, as 'suspected multiple sclerosis' is explicitly excluded.</t>
+  </si>
+  <si>
+    <t>GitHub (https://github.com/spiros/chronological-map-phenotypes/tree/master/primary_care)</t>
+  </si>
+  <si>
+    <t>One codelist from https://github.com/spiros/chronological-map-phenotypes/tree/master/primary_care</t>
+  </si>
+  <si>
+    <t>Manual classification of terms found in the dictionary, ensuring only definite multiple sclerosis codes are included and others (e.g., suspected, administrative) are excluded.</t>
+  </si>
+  <si>
+    <t>Yes, one existing codelist from https://github.com/spiros/chronological-map-phenotypes/tree/master/primary_care was used as a basis/starting point for this codelist.</t>
+  </si>
+  <si>
+    <t>The primary search term was `*multiple*sclerosis*`. Other explicit synonyms or sources of clinical knowledge for identifying them beyond the initial base codelist are not defined.</t>
+  </si>
+  <si>
+    <t>Neonatal multiple sclerosis, family history of multiple sclerosis, suspected multiple sclerosis, multiple sclerosis care plan agreed, multiple sclerosis monitoring letters/invitations, referral by MS nurse, Kurtzke rating scale, questionnaire completed, referral to community MS team.</t>
+  </si>
+  <si>
+    <t>A Stata script was used to perform a word search in the medical dictionary, followed by manual classification of identified terms.</t>
+  </si>
+  <si>
+    <t>Search term: `*multiple*sclerosis*`. Exclusion terms: `*neonatal*`, `*fh:*`, `*family*history*`, and specific manual exclusions like 'suspected multiple sclerosis'.</t>
+  </si>
+  <si>
+    <t>Terms identified by the word search were manually reviewed and categorized as definite multiple sclerosis (included) or non-definite/administrative (excluded). Examples include explicitly excluding 'suspected multiple sclerosis' and including various definite forms like 'relapsing remitting multiple sclerosis'.</t>
+  </si>
+  <si>
+    <t>An `assert` command was used in the Stata script to ensure all identified terms were classified. However, no specific findings regarding prevalence or incidence within the dataset for the final codelist are reported.</t>
+  </si>
+  <si>
+    <t>No external checks performed.</t>
+  </si>
+  <si>
+    <t>Smoking status codelist for CPRD Aurum</t>
+  </si>
+  <si>
+    <t>Smoking status and related concepts (e.g., tobacco dependence, smoking cessation therapy)</t>
+  </si>
+  <si>
+    <t>Current and previous events, categorized into non-smoker, current smoker, and ex-smoker statuses.</t>
+  </si>
+  <si>
+    <t>Primarily definite codes, categorized into non-smoker, current smoker, ex-smoker, and current/ex-smoker statuses.</t>
+  </si>
+  <si>
+    <t>The CPRDAurumMedical dictionary was searched for relevant terms.</t>
+  </si>
+  <si>
+    <t>An existing codelist named 'smoking_aurum_achim' (presumably from Helen) was identified and used for comparison.</t>
+  </si>
+  <si>
+    <t>The codelist was cross-checked against 'smoking_aurum_achim'. No explicit external verification information for 'smoking_aurum_achim' itself is provided.</t>
+  </si>
+  <si>
+    <t>Manual review and categorization of individual terms were conducted. An assertion was used to check that all identified codes were classified.</t>
+  </si>
+  <si>
+    <t>Yes, an existing codelist named 'smoking_aurum_achim' was used to cross-check the newly created codelist categories.</t>
+  </si>
+  <si>
+    <t>Keywords used for initial term identification include TOBACCO, NICOTINE, SMOK, CIGAR, BUPROPION, and PACK YEARS. These were identified through keyword search in the CPRDAurumMedical dictionary terms.</t>
+  </si>
+  <si>
+    <t>Codes related to smoke inhalation, passive smoking, family history of smoking, adverse reactions to nicotine/bupropion not linked to cessation, smoke alarms, tobacco industry roles, and general exposure to smoke/fire were excluded.</t>
+  </si>
+  <si>
+    <t>A Stata script was used to identify terms by keywords, followed by manual categorization and refinement based on specific term matching.</t>
+  </si>
+  <si>
+    <t>Search terms: TOBACCO, NICOTINE, SMOK, CIGAR, BUPROPION, PACK YEARS. Exclusion terms were implicitly defined by terms assigned as irrelevant (type=9) during manual review.</t>
+  </si>
+  <si>
+    <t>No, the search was based on keywords and explicit term matching rather than dictionary hierarchy.</t>
+  </si>
+  <si>
+    <t>Terms were iteratively reviewed and manually assigned to categories (non-smoker, current smoker, ex-smoker, current/ex-smoker, or irrelevant) based on their clinical meaning. New codes were classified as they appeared during review.</t>
   </si>
   <si>
     <t xml:space="preserve"> (Optional) Categories </t>
   </si>
   <si>
-    <t xml:space="preserve">Yes, subcategories include 'non-smoker' (0), 'current smoker' (1), 'ex-smoker' (2), and 'current or ex-smoker' (12).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal comparison was made with a codelist from 'Helen' (implied internal reviewer/collaborator). No explicit external reviewers are documented for this specific codelist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The draft codelist and its categorization were compared against an existing codelist ('smoking_aurum_achim') to identify discrepancies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The review process is documented in the Stata script comments (comparison with an existing codelist).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An assertion ('assert smokstatus!=.') was used to confirm that all codes were classified into a smoking status category. Irrelevant codes (type=9) were dropped. No findings on observation counts are provided in the Stata code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not defined (saved locally to '$codelists/cr_codelist_smoking_aurum')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stata script used for codelist creation (locally stored).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codelist_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_asthma_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_bmi_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_bronchiectasis_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_copd_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_cvdgrouped_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_diabetes_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_hypertension_medical_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_ild_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_multiple_sclerosis_aurum.do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr_codelist_smoking_aurum.do</t>
+    <t>Yes, subcategories include 'non-smoker' (0), 'current smoker' (1), 'ex-smoker' (2), and 'current or ex-smoker' (12).</t>
+  </si>
+  <si>
+    <t>Internal comparison was made with a codelist from 'Helen' (implied internal reviewer/collaborator). No explicit external reviewers are documented for this specific codelist.</t>
+  </si>
+  <si>
+    <t>The draft codelist and its categorization were compared against an existing codelist ('smoking_aurum_achim') to identify discrepancies.</t>
+  </si>
+  <si>
+    <t>The review process is documented in the Stata script comments (comparison with an existing codelist).</t>
+  </si>
+  <si>
+    <t>An assertion ('assert smokstatus!=.') was used to confirm that all codes were classified into a smoking status category. Irrelevant codes (type=9) were dropped. No findings on observation counts are provided in the Stata code.</t>
+  </si>
+  <si>
+    <t>not defined (saved locally to '$codelists/cr_codelist_smoking_aurum')</t>
+  </si>
+  <si>
+    <t>Stata script used for codelist creation (locally stored).</t>
+  </si>
+  <si>
+    <t>codelist_file</t>
+  </si>
+  <si>
+    <t>cr_codelist_asthma_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_bmi_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_bronchiectasis_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_copd_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_cvdgrouped_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_diabetes_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_hypertension_medical_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_ild_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_multiple_sclerosis_aurum.do</t>
+  </si>
+  <si>
+    <t>cr_codelist_smoking_aurum.do</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1136,170 +1143,179 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="information"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Table12" displayName="Table12" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table11" displayName="Table11" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Table13" displayName="Table13" ref="A1:G281" totalsRowShown="0">
+  <autoFilter ref="A1:G281" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="information"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0A00-000007000000}" name="codelist_file"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table12" displayName="Table12" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table4" displayName="Table4" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table13" displayName="Table13" ref="A1:G281" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G281"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
-    <tableColumn id="7" name="codelist_file"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table5" displayName="Table5" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table6" displayName="Table6" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table7" displayName="Table7" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table8" displayName="Table8" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table9" displayName="Table9" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table10" displayName="Table10" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:F29" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table11" displayName="Table11" ref="A1:F29" totalsRowShown="0">
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="header"/>
-    <tableColumn id="2" name="subheader"/>
-    <tableColumn id="3" name="step"/>
-    <tableColumn id="4" name="item_name"/>
-    <tableColumn id="5" name="description"/>
-    <tableColumn id="6" name="information"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="header"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="subheader"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="step"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="item_name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="information"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1583,19 +1599,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="21.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="146.1796875" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1615,7 +1631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1635,7 +1651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1655,7 +1671,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1675,7 +1691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1695,7 +1711,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1715,7 +1731,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1735,7 +1751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1755,7 +1771,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1775,7 +1791,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1795,7 +1811,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1815,7 +1831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1835,7 +1851,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1855,7 +1871,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1875,7 +1891,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1895,7 +1911,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -1915,7 +1931,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -1935,7 +1951,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -1955,7 +1971,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -1975,7 +1991,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1995,7 +2011,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -2015,7 +2031,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -2035,7 +2051,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -2055,7 +2071,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -2075,7 +2091,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -2095,7 +2111,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -2115,7 +2131,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -2135,7 +2151,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -2155,7 +2171,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -2177,27 +2193,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="236.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="236.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2217,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2237,7 +2253,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2257,7 +2273,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2277,7 +2293,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2297,7 +2313,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2317,7 +2333,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -2337,7 +2353,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2357,7 +2373,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -2377,7 +2393,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2397,7 +2413,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -2417,7 +2433,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -2437,7 +2453,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -2457,7 +2473,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -2477,7 +2493,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -2497,7 +2513,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -2517,7 +2533,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -2537,7 +2553,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -2557,7 +2573,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -2577,7 +2593,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -2597,7 +2613,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -2617,7 +2633,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -2637,7 +2653,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -2657,7 +2673,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -2677,7 +2693,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -2697,7 +2713,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -2717,7 +2733,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -2737,7 +2753,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -2757,7 +2773,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -2779,28 +2795,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:G281"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="174.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="41.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="174.7265625" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
+    <col min="7" max="7" width="41.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2823,7 +2839,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2846,7 +2862,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2869,7 +2885,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2892,7 +2908,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2915,7 +2931,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2938,7 +2954,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -2961,7 +2977,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2984,7 +3000,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -3007,7 +3023,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -3030,7 +3046,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -3053,7 +3069,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -3076,7 +3092,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -3099,7 +3115,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -3122,7 +3138,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -3145,7 +3161,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -3168,7 +3184,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3191,7 +3207,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -3214,7 +3230,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -3237,7 +3253,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -3260,7 +3276,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -3283,7 +3299,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -3306,7 +3322,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -3329,7 +3345,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -3352,7 +3368,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -3375,7 +3391,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -3398,7 +3414,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -3421,7 +3437,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -3444,7 +3460,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -3467,7 +3483,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -3490,7 +3506,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -3513,7 +3529,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -3536,7 +3552,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -3559,7 +3575,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -3582,7 +3598,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -3605,7 +3621,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -3628,7 +3644,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -3651,7 +3667,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -3674,7 +3690,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -3697,7 +3713,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -3720,7 +3736,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -3743,7 +3759,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -3766,7 +3782,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -3789,7 +3805,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -3812,7 +3828,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>67</v>
       </c>
@@ -3835,7 +3851,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -3858,7 +3874,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -3881,7 +3897,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>67</v>
       </c>
@@ -3904,7 +3920,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>67</v>
       </c>
@@ -3927,7 +3943,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -3950,7 +3966,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -3973,7 +3989,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -3996,7 +4012,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -4019,7 +4035,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -4042,7 +4058,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -4065,7 +4081,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -4088,7 +4104,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -4111,7 +4127,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -4134,7 +4150,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -4157,7 +4173,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -4180,7 +4196,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -4203,7 +4219,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -4226,7 +4242,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>27</v>
       </c>
@@ -4249,7 +4265,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>27</v>
       </c>
@@ -4272,7 +4288,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>27</v>
       </c>
@@ -4295,7 +4311,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -4318,7 +4334,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>44</v>
       </c>
@@ -4341,7 +4357,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>44</v>
       </c>
@@ -4364,7 +4380,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>44</v>
       </c>
@@ -4387,7 +4403,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>44</v>
       </c>
@@ -4410,7 +4426,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>44</v>
       </c>
@@ -4433,7 +4449,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>67</v>
       </c>
@@ -4456,7 +4472,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>67</v>
       </c>
@@ -4479,7 +4495,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>67</v>
       </c>
@@ -4502,7 +4518,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>67</v>
       </c>
@@ -4525,7 +4541,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>67</v>
       </c>
@@ -4548,7 +4564,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>67</v>
       </c>
@@ -4571,7 +4587,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>67</v>
       </c>
@@ -4594,7 +4610,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>98</v>
       </c>
@@ -4617,7 +4633,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>98</v>
       </c>
@@ -4640,7 +4656,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>98</v>
       </c>
@@ -4663,7 +4679,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>98</v>
       </c>
@@ -4686,7 +4702,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>98</v>
       </c>
@@ -4709,7 +4725,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -4732,7 +4748,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>98</v>
       </c>
@@ -4755,7 +4771,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -4778,7 +4794,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -4801,7 +4817,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -4824,7 +4840,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -4847,7 +4863,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -4870,7 +4886,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>27</v>
       </c>
@@ -4893,7 +4909,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>27</v>
       </c>
@@ -4916,7 +4932,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>27</v>
       </c>
@@ -4939,7 +4955,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>27</v>
       </c>
@@ -4962,7 +4978,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>44</v>
       </c>
@@ -4985,7 +5001,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>44</v>
       </c>
@@ -5008,7 +5024,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>44</v>
       </c>
@@ -5031,7 +5047,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -5054,7 +5070,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>44</v>
       </c>
@@ -5077,7 +5093,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>67</v>
       </c>
@@ -5100,7 +5116,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>67</v>
       </c>
@@ -5123,7 +5139,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>67</v>
       </c>
@@ -5146,7 +5162,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>67</v>
       </c>
@@ -5169,7 +5185,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>67</v>
       </c>
@@ -5192,7 +5208,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>67</v>
       </c>
@@ -5215,7 +5231,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>67</v>
       </c>
@@ -5238,7 +5254,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>98</v>
       </c>
@@ -5261,7 +5277,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>98</v>
       </c>
@@ -5284,7 +5300,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>98</v>
       </c>
@@ -5307,7 +5323,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>98</v>
       </c>
@@ -5330,7 +5346,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>98</v>
       </c>
@@ -5353,7 +5369,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>98</v>
       </c>
@@ -5376,7 +5392,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>98</v>
       </c>
@@ -5399,7 +5415,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -5422,7 +5438,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -5445,7 +5461,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>6</v>
       </c>
@@ -5468,7 +5484,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>6</v>
       </c>
@@ -5491,7 +5507,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>6</v>
       </c>
@@ -5514,7 +5530,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>27</v>
       </c>
@@ -5537,7 +5553,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>27</v>
       </c>
@@ -5560,7 +5576,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>27</v>
       </c>
@@ -5583,7 +5599,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>27</v>
       </c>
@@ -5606,7 +5622,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>44</v>
       </c>
@@ -5629,7 +5645,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>44</v>
       </c>
@@ -5652,7 +5668,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>44</v>
       </c>
@@ -5675,7 +5691,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>44</v>
       </c>
@@ -5698,7 +5714,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>44</v>
       </c>
@@ -5721,7 +5737,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>67</v>
       </c>
@@ -5744,7 +5760,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>67</v>
       </c>
@@ -5767,7 +5783,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>67</v>
       </c>
@@ -5790,7 +5806,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>67</v>
       </c>
@@ -5813,7 +5829,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>67</v>
       </c>
@@ -5836,7 +5852,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>67</v>
       </c>
@@ -5859,7 +5875,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>67</v>
       </c>
@@ -5882,7 +5898,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>98</v>
       </c>
@@ -5905,7 +5921,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>98</v>
       </c>
@@ -5928,7 +5944,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>98</v>
       </c>
@@ -5951,7 +5967,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>98</v>
       </c>
@@ -5974,7 +5990,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>98</v>
       </c>
@@ -5997,7 +6013,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>98</v>
       </c>
@@ -6020,7 +6036,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>98</v>
       </c>
@@ -6043,7 +6059,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>248</v>
       </c>
@@ -6066,7 +6082,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>248</v>
       </c>
@@ -6089,7 +6105,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>248</v>
       </c>
@@ -6112,7 +6128,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>248</v>
       </c>
@@ -6135,7 +6151,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>248</v>
       </c>
@@ -6158,7 +6174,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>252</v>
       </c>
@@ -6181,7 +6197,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>252</v>
       </c>
@@ -6204,7 +6220,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>252</v>
       </c>
@@ -6227,7 +6243,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>252</v>
       </c>
@@ -6250,7 +6266,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>256</v>
       </c>
@@ -6273,7 +6289,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>256</v>
       </c>
@@ -6296,7 +6312,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>256</v>
       </c>
@@ -6319,7 +6335,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>256</v>
       </c>
@@ -6342,7 +6358,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>256</v>
       </c>
@@ -6365,7 +6381,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>263</v>
       </c>
@@ -6388,7 +6404,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>263</v>
       </c>
@@ -6411,7 +6427,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>263</v>
       </c>
@@ -6434,7 +6450,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>263</v>
       </c>
@@ -6457,7 +6473,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>263</v>
       </c>
@@ -6480,7 +6496,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>263</v>
       </c>
@@ -6503,7 +6519,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>263</v>
       </c>
@@ -6526,7 +6542,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>98</v>
       </c>
@@ -6549,7 +6565,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>98</v>
       </c>
@@ -6572,7 +6588,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>98</v>
       </c>
@@ -6595,7 +6611,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>98</v>
       </c>
@@ -6618,7 +6634,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>98</v>
       </c>
@@ -6641,7 +6657,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>98</v>
       </c>
@@ -6664,7 +6680,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>98</v>
       </c>
@@ -6687,7 +6703,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -6710,7 +6726,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -6733,7 +6749,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -6756,7 +6772,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -6779,7 +6795,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -6802,7 +6818,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>27</v>
       </c>
@@ -6825,7 +6841,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>27</v>
       </c>
@@ -6848,7 +6864,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>27</v>
       </c>
@@ -6871,7 +6887,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>27</v>
       </c>
@@ -6894,7 +6910,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>44</v>
       </c>
@@ -6917,7 +6933,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>44</v>
       </c>
@@ -6940,7 +6956,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>44</v>
       </c>
@@ -6963,7 +6979,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>44</v>
       </c>
@@ -6986,7 +7002,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>44</v>
       </c>
@@ -7009,7 +7025,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>67</v>
       </c>
@@ -7032,7 +7048,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>67</v>
       </c>
@@ -7055,7 +7071,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>67</v>
       </c>
@@ -7078,7 +7094,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>67</v>
       </c>
@@ -7101,7 +7117,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>67</v>
       </c>
@@ -7124,7 +7140,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>67</v>
       </c>
@@ -7147,7 +7163,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>67</v>
       </c>
@@ -7170,7 +7186,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>98</v>
       </c>
@@ -7193,7 +7209,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>98</v>
       </c>
@@ -7216,7 +7232,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>98</v>
       </c>
@@ -7239,7 +7255,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>98</v>
       </c>
@@ -7262,7 +7278,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>98</v>
       </c>
@@ -7285,7 +7301,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>98</v>
       </c>
@@ -7308,7 +7324,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>98</v>
       </c>
@@ -7331,7 +7347,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -7354,7 +7370,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>6</v>
       </c>
@@ -7377,7 +7393,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>6</v>
       </c>
@@ -7400,7 +7416,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>6</v>
       </c>
@@ -7423,7 +7439,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>6</v>
       </c>
@@ -7446,7 +7462,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>27</v>
       </c>
@@ -7469,7 +7485,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>27</v>
       </c>
@@ -7492,7 +7508,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>27</v>
       </c>
@@ -7515,7 +7531,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>27</v>
       </c>
@@ -7538,7 +7554,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>44</v>
       </c>
@@ -7561,7 +7577,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>44</v>
       </c>
@@ -7584,7 +7600,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>44</v>
       </c>
@@ -7607,7 +7623,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>44</v>
       </c>
@@ -7630,7 +7646,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>44</v>
       </c>
@@ -7653,7 +7669,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>67</v>
       </c>
@@ -7676,7 +7692,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>67</v>
       </c>
@@ -7699,7 +7715,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>67</v>
       </c>
@@ -7722,7 +7738,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>67</v>
       </c>
@@ -7745,7 +7761,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>67</v>
       </c>
@@ -7768,7 +7784,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>67</v>
       </c>
@@ -7791,7 +7807,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -7814,7 +7830,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>98</v>
       </c>
@@ -7837,7 +7853,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>98</v>
       </c>
@@ -7860,7 +7876,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>98</v>
       </c>
@@ -7883,7 +7899,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -7906,7 +7922,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>98</v>
       </c>
@@ -7929,7 +7945,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>98</v>
       </c>
@@ -7952,7 +7968,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>98</v>
       </c>
@@ -7975,7 +7991,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -7998,7 +8014,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -8021,7 +8037,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -8044,7 +8060,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>6</v>
       </c>
@@ -8067,7 +8083,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -8090,7 +8106,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>27</v>
       </c>
@@ -8113,7 +8129,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>27</v>
       </c>
@@ -8136,7 +8152,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>27</v>
       </c>
@@ -8159,7 +8175,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>27</v>
       </c>
@@ -8182,7 +8198,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>44</v>
       </c>
@@ -8205,7 +8221,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>44</v>
       </c>
@@ -8228,7 +8244,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>44</v>
       </c>
@@ -8251,7 +8267,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>44</v>
       </c>
@@ -8274,7 +8290,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -8297,7 +8313,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>67</v>
       </c>
@@ -8320,7 +8336,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>67</v>
       </c>
@@ -8343,7 +8359,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>67</v>
       </c>
@@ -8366,7 +8382,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>67</v>
       </c>
@@ -8389,7 +8405,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>67</v>
       </c>
@@ -8412,7 +8428,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>67</v>
       </c>
@@ -8435,7 +8451,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>67</v>
       </c>
@@ -8458,7 +8474,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>98</v>
       </c>
@@ -8481,7 +8497,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>98</v>
       </c>
@@ -8504,7 +8520,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>98</v>
       </c>
@@ -8527,7 +8543,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>98</v>
       </c>
@@ -8550,7 +8566,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>98</v>
       </c>
@@ -8573,7 +8589,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>98</v>
       </c>
@@ -8596,7 +8612,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>98</v>
       </c>
@@ -8619,7 +8635,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -8642,7 +8658,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -8665,7 +8681,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -8688,7 +8704,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -8711,7 +8727,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>6</v>
       </c>
@@ -8734,7 +8750,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>27</v>
       </c>
@@ -8757,7 +8773,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>27</v>
       </c>
@@ -8780,7 +8796,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>27</v>
       </c>
@@ -8803,7 +8819,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>27</v>
       </c>
@@ -8826,7 +8842,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>44</v>
       </c>
@@ -8849,7 +8865,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>44</v>
       </c>
@@ -8872,7 +8888,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>44</v>
       </c>
@@ -8895,7 +8911,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>44</v>
       </c>
@@ -8918,7 +8934,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>44</v>
       </c>
@@ -8941,7 +8957,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>67</v>
       </c>
@@ -8964,7 +8980,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>67</v>
       </c>
@@ -8987,7 +9003,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>67</v>
       </c>
@@ -9010,7 +9026,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>67</v>
       </c>
@@ -9033,7 +9049,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>67</v>
       </c>
@@ -9056,7 +9072,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>67</v>
       </c>
@@ -9079,7 +9095,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>67</v>
       </c>
@@ -9102,7 +9118,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>98</v>
       </c>
@@ -9125,7 +9141,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>98</v>
       </c>
@@ -9148,7 +9164,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>98</v>
       </c>
@@ -9171,7 +9187,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>98</v>
       </c>
@@ -9194,7 +9210,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>98</v>
       </c>
@@ -9217,7 +9233,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>98</v>
       </c>
@@ -9240,7 +9256,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>98</v>
       </c>
@@ -9265,27 +9281,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="32.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="231.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="32.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="231.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9305,7 +9321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9325,7 +9341,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -9345,7 +9361,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -9365,7 +9381,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -9385,7 +9401,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -9405,7 +9421,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -9425,7 +9441,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -9445,9 +9461,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>27</v>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -9465,7 +9481,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -9485,7 +9501,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -9505,7 +9521,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -9525,7 +9541,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -9545,7 +9561,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -9565,7 +9581,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -9585,7 +9601,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -9605,7 +9621,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -9625,7 +9641,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -9645,7 +9661,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -9665,7 +9681,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -9685,7 +9701,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -9705,7 +9721,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -9725,7 +9741,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -9745,7 +9761,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -9765,7 +9781,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -9785,7 +9801,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -9805,7 +9821,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -9825,7 +9841,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -9845,7 +9861,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -9867,27 +9883,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="174.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="174.7265625" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9907,7 +9923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -9927,7 +9943,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -9947,7 +9963,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -9967,7 +9983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -9987,7 +10003,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -10007,7 +10023,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -10027,7 +10043,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -10047,7 +10063,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -10067,7 +10083,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -10087,7 +10103,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -10107,7 +10123,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -10127,7 +10143,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -10147,7 +10163,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -10167,7 +10183,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -10187,7 +10203,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -10207,7 +10223,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -10227,7 +10243,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -10247,7 +10263,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -10267,7 +10283,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -10287,7 +10303,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -10307,7 +10323,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -10327,7 +10343,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -10347,7 +10363,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -10367,7 +10383,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -10387,7 +10403,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -10407,7 +10423,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -10427,7 +10443,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -10447,7 +10463,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -10469,27 +10485,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10509,7 +10525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -10529,7 +10545,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -10549,7 +10565,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -10569,7 +10585,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -10589,7 +10605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -10609,7 +10625,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -10629,7 +10645,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -10649,7 +10665,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -10669,7 +10685,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -10689,7 +10705,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -10709,7 +10725,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -10729,7 +10745,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -10749,7 +10765,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -10769,7 +10785,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -10789,7 +10805,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -10809,7 +10825,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -10829,7 +10845,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -10849,7 +10865,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -10869,7 +10885,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -10889,7 +10905,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -10909,7 +10925,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -10929,7 +10945,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -10949,7 +10965,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -10969,7 +10985,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -10989,7 +11005,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -11009,7 +11025,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -11029,7 +11045,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -11049,7 +11065,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -11071,27 +11087,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="32.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="32.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11111,7 +11127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -11131,7 +11147,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -11151,7 +11167,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -11171,7 +11187,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -11191,7 +11207,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -11211,7 +11227,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -11231,7 +11247,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -11251,7 +11267,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -11271,7 +11287,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -11291,7 +11307,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -11311,7 +11327,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -11331,7 +11347,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -11351,7 +11367,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -11371,7 +11387,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -11391,7 +11407,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -11411,7 +11427,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -11431,7 +11447,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -11451,7 +11467,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -11471,7 +11487,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -11491,7 +11507,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -11511,7 +11527,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -11531,7 +11547,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -11551,7 +11567,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -11571,7 +11587,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -11591,7 +11607,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -11611,7 +11627,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -11631,7 +11647,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -11651,7 +11667,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -11673,27 +11689,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="32.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.7265625" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="32.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11713,7 +11729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>248</v>
       </c>
@@ -11733,7 +11749,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>248</v>
       </c>
@@ -11753,7 +11769,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>248</v>
       </c>
@@ -11773,7 +11789,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>248</v>
       </c>
@@ -11793,7 +11809,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>248</v>
       </c>
@@ -11813,7 +11829,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>252</v>
       </c>
@@ -11833,7 +11849,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>252</v>
       </c>
@@ -11853,7 +11869,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>252</v>
       </c>
@@ -11873,7 +11889,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>252</v>
       </c>
@@ -11893,7 +11909,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>256</v>
       </c>
@@ -11913,7 +11929,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>256</v>
       </c>
@@ -11933,7 +11949,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>256</v>
       </c>
@@ -11953,7 +11969,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>256</v>
       </c>
@@ -11973,7 +11989,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>256</v>
       </c>
@@ -11993,7 +12009,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>263</v>
       </c>
@@ -12013,7 +12029,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>263</v>
       </c>
@@ -12033,7 +12049,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>263</v>
       </c>
@@ -12053,7 +12069,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>263</v>
       </c>
@@ -12073,7 +12089,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>263</v>
       </c>
@@ -12093,7 +12109,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>263</v>
       </c>
@@ -12113,7 +12129,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>263</v>
       </c>
@@ -12133,7 +12149,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -12153,7 +12169,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -12173,7 +12189,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -12193,7 +12209,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -12213,7 +12229,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -12233,7 +12249,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -12253,7 +12269,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -12275,27 +12291,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="32.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="32.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12315,7 +12331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -12335,7 +12351,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -12355,7 +12371,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -12375,7 +12391,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -12395,7 +12411,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -12415,7 +12431,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -12435,7 +12451,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -12455,7 +12471,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -12475,7 +12491,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -12495,7 +12511,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -12515,7 +12531,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -12535,7 +12551,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -12555,7 +12571,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -12575,7 +12591,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -12595,7 +12611,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -12615,7 +12631,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -12635,7 +12651,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -12655,7 +12671,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -12675,7 +12691,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -12695,7 +12711,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -12715,7 +12731,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -12735,7 +12751,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -12755,7 +12771,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -12775,7 +12791,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -12795,7 +12811,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -12815,7 +12831,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -12835,7 +12851,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -12855,7 +12871,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -12877,27 +12893,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="219.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="219.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12917,7 +12933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -12937,7 +12953,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -12957,7 +12973,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -12977,7 +12993,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -12997,7 +13013,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -13017,7 +13033,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -13037,7 +13053,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -13057,7 +13073,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -13077,7 +13093,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -13097,7 +13113,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -13117,7 +13133,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -13137,7 +13153,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -13157,7 +13173,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -13177,7 +13193,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -13197,7 +13213,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -13217,7 +13233,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -13237,7 +13253,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -13257,7 +13273,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -13277,7 +13293,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -13297,7 +13313,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -13317,7 +13333,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -13337,7 +13353,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -13357,7 +13373,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -13377,7 +13393,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -13397,7 +13413,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -13417,7 +13433,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -13437,7 +13453,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -13457,7 +13473,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -13479,27 +13495,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="173.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="41.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="173.7265625" customWidth="1"/>
+    <col min="6" max="6" width="250.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13519,7 +13535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -13539,7 +13555,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -13559,7 +13575,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -13579,7 +13595,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -13599,7 +13615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -13619,7 +13635,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -13639,7 +13655,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -13659,7 +13675,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -13679,7 +13695,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -13699,7 +13715,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -13719,7 +13735,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -13739,7 +13755,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -13759,7 +13775,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -13779,7 +13795,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -13799,7 +13815,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -13819,7 +13835,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -13839,7 +13855,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -13859,7 +13875,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -13879,7 +13895,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -13899,7 +13915,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -13919,7 +13935,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -13939,7 +13955,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -13959,7 +13975,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -13979,7 +13995,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>98</v>
       </c>
@@ -13999,7 +14015,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>98</v>
       </c>
@@ -14019,7 +14035,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -14039,7 +14055,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -14059,7 +14075,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -14081,9 +14097,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>